--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\ETCHE-LAI-Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728D0B32-F1CA-4F25-919F-F1CB88F52F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE337CBF-06F0-40F0-961B-8655422FD985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frontend" sheetId="8" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="146">
   <si>
     <t>L_den</t>
   </si>
@@ -538,6 +538,12 @@
   </si>
   <si>
     <t>Threshold?</t>
+  </si>
+  <si>
+    <t>in Annex 4: "All estimates are per person and per year" -&gt; also noch Multiplikation mit Personen/ Exponierten/ Bundesdeutsche Bevölkerung notwendig?</t>
+  </si>
+  <si>
+    <t>YYL/ YLD für  mortality, CVD, Diabetes, IHD nach 2019 GBD</t>
   </si>
 </sst>
 </file>
@@ -737,7 +743,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -829,6 +835,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1352,15 +1363,15 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
     </row>
     <row r="8" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1369,29 +1380,29 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="56"/>
+      <c r="B10" s="59"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="J12" s="57" t="s">
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="J12" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="57"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+      <c r="O12" s="60"/>
     </row>
     <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
@@ -1432,7 +1443,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="61" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
@@ -1479,7 +1490,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
+      <c r="A15" s="61"/>
       <c r="B15" t="s">
         <v>84</v>
       </c>
@@ -1554,7 +1565,7 @@
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="58" t="s">
+      <c r="A18" s="61" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
@@ -1601,7 +1612,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="58"/>
+      <c r="A19" s="61"/>
       <c r="B19" t="s">
         <v>80</v>
       </c>
@@ -1676,7 +1687,7 @@
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="61" t="s">
         <v>81</v>
       </c>
       <c r="B22" t="s">
@@ -1723,7 +1734,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="58"/>
+      <c r="A23" s="61"/>
       <c r="B23" t="s">
         <v>83</v>
       </c>
@@ -1774,10 +1785,10 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="56"/>
+      <c r="B32" s="59"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -2354,21 +2365,21 @@
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="D40" s="61" t="s">
+      <c r="D40" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61" t="s">
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
-      <c r="N40" s="61"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="64"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
@@ -2409,14 +2420,14 @@
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="56" t="s">
         <v>85</v>
       </c>
       <c r="C42" s="20"/>
-      <c r="D42" s="21">
+      <c r="D42" s="57">
         <f>SUM(E42:O42)</f>
         <v>20796420.796399999</v>
       </c>
@@ -2471,7 +2482,7 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="64"/>
+      <c r="A43" s="67"/>
       <c r="B43" s="15" t="s">
         <v>110</v>
       </c>
@@ -2512,7 +2523,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="63"/>
+      <c r="A44" s="66"/>
       <c r="B44" s="16" t="s">
         <v>111</v>
       </c>
@@ -2575,7 +2586,7 @@
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="62" t="s">
+      <c r="A46" s="65" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="19" t="s">
@@ -2629,7 +2640,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="64"/>
+      <c r="A47" s="67"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
@@ -2650,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="24">
-        <f t="shared" si="3"/>
+        <f>G44*(G46-1)</f>
         <v>0</v>
       </c>
       <c r="H47" s="24">
@@ -2687,7 +2698,7 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="64"/>
+      <c r="A48" s="67"/>
       <c r="B48" s="15" t="s">
         <v>113</v>
       </c>
@@ -2712,7 +2723,7 @@
       <c r="O48" s="15"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="63"/>
+      <c r="A49" s="66"/>
       <c r="B49" s="22" t="s">
         <v>90</v>
       </c>
@@ -2737,7 +2748,7 @@
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="62" t="s">
+      <c r="A50" s="65" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="19" t="s">
@@ -2791,7 +2802,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="64"/>
+      <c r="A51" s="67"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
@@ -2849,7 +2860,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="64"/>
+      <c r="A52" s="67"/>
       <c r="B52" s="15" t="s">
         <v>113</v>
       </c>
@@ -2874,7 +2885,7 @@
       <c r="O52" s="15"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="63"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="22" t="s">
         <v>137</v>
       </c>
@@ -2899,7 +2910,7 @@
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="62" t="s">
+      <c r="A54" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="19" t="s">
@@ -2953,7 +2964,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="64"/>
+      <c r="A55" s="67"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
@@ -3011,7 +3022,7 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="64"/>
+      <c r="A56" s="67"/>
       <c r="B56" s="15" t="s">
         <v>113</v>
       </c>
@@ -3036,7 +3047,7 @@
       <c r="O56" s="15"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="63"/>
+      <c r="A57" s="66"/>
       <c r="B57" s="22" t="s">
         <v>138</v>
       </c>
@@ -3061,7 +3072,7 @@
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="62" t="s">
+      <c r="A58" s="65" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="19" t="s">
@@ -3115,7 +3126,7 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="64"/>
+      <c r="A59" s="67"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
@@ -3173,7 +3184,7 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="64"/>
+      <c r="A60" s="67"/>
       <c r="B60" s="15" t="s">
         <v>113</v>
       </c>
@@ -3198,7 +3209,7 @@
       <c r="O60" s="15"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="63"/>
+      <c r="A61" s="66"/>
       <c r="B61" s="22" t="s">
         <v>139</v>
       </c>
@@ -3223,7 +3234,7 @@
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="62" t="s">
+      <c r="A62" s="65" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -3275,7 +3286,7 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="58"/>
+      <c r="A63" s="61"/>
       <c r="B63" s="34" t="s">
         <v>114</v>
       </c>
@@ -3325,7 +3336,7 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="58"/>
+      <c r="A64" s="61"/>
       <c r="B64" s="15" t="s">
         <v>113</v>
       </c>
@@ -3340,7 +3351,7 @@
       <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="63"/>
+      <c r="A65" s="66"/>
       <c r="B65" s="47" t="s">
         <v>96</v>
       </c>
@@ -3441,7 +3452,7 @@
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="62" t="s">
+      <c r="A69" s="65" t="s">
         <v>104</v>
       </c>
       <c r="B69" s="20" t="s">
@@ -3495,7 +3506,7 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="64"/>
+      <c r="A70" s="67"/>
       <c r="B70" s="15" t="s">
         <v>110</v>
       </c>
@@ -3534,7 +3545,7 @@
       <c r="O70" s="15"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="63"/>
+      <c r="A71" s="66"/>
       <c r="B71" s="16" t="s">
         <v>111</v>
       </c>
@@ -3606,7 +3617,7 @@
       <c r="O72" s="15"/>
     </row>
     <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="59" t="s">
+      <c r="A73" s="62" t="s">
         <v>53</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -3654,7 +3665,7 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="59"/>
+      <c r="A74" s="62"/>
       <c r="B74" s="34" t="s">
         <v>114</v>
       </c>
@@ -3700,7 +3711,7 @@
       </c>
     </row>
     <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="59"/>
+      <c r="A75" s="62"/>
       <c r="B75" s="15" t="s">
         <v>113</v>
       </c>
@@ -3714,7 +3725,7 @@
       </c>
     </row>
     <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="60"/>
+      <c r="A76" s="63"/>
       <c r="B76" s="47" t="s">
         <v>96</v>
       </c>
@@ -3811,7 +3822,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64" bestFit="1" customWidth="1"/>
@@ -3871,6 +3882,17 @@
       </c>
       <c r="C5" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="55">
+        <v>5</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -5,25 +5,26 @@
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\ETCHE-LAI-Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE337CBF-06F0-40F0-961B-8655422FD985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5169092-D08D-4B8E-B38D-02AC05C49E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frontend" sheetId="8" r:id="rId1"/>
     <sheet name="Agglomeration road" sheetId="1" r:id="rId2"/>
-    <sheet name="Fragen" sheetId="11" r:id="rId3"/>
-    <sheet name="ERF HRA" sheetId="10" r:id="rId4"/>
-    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId5"/>
-    <sheet name="Agglomeration rail" sheetId="2" r:id="rId6"/>
-    <sheet name="Agglomeration air" sheetId="3" r:id="rId7"/>
-    <sheet name="Agglomeration industry" sheetId="4" r:id="rId8"/>
-    <sheet name="Major roads " sheetId="5" r:id="rId9"/>
-    <sheet name="Major railways " sheetId="6" r:id="rId10"/>
-    <sheet name="Major airports" sheetId="7" r:id="rId11"/>
+    <sheet name="Agglomeration road (YLL_YLD)" sheetId="12" r:id="rId3"/>
+    <sheet name="Fragen" sheetId="11" r:id="rId4"/>
+    <sheet name="ERF HRA" sheetId="10" r:id="rId5"/>
+    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId6"/>
+    <sheet name="Agglomeration rail" sheetId="2" r:id="rId7"/>
+    <sheet name="Agglomeration air" sheetId="3" r:id="rId8"/>
+    <sheet name="Agglomeration industry" sheetId="4" r:id="rId9"/>
+    <sheet name="Major roads " sheetId="5" r:id="rId10"/>
+    <sheet name="Major railways " sheetId="6" r:id="rId11"/>
+    <sheet name="Major airports" sheetId="7" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="149">
   <si>
     <t>L_den</t>
   </si>
@@ -544,6 +545,15 @@
   </si>
   <si>
     <t>YYL/ YLD für  mortality, CVD, Diabetes, IHD nach 2019 GBD</t>
+  </si>
+  <si>
+    <t>YLL = YLLnat (= 0,2069215) ∙ Aftot *  69.411.087</t>
+  </si>
+  <si>
+    <t>YLD = YLD of the disease (= 0,0115708) * Aftot *  69.411.087</t>
+  </si>
+  <si>
+    <t>YLD = YLD of the disease (= 0,0059261) * Aftot *  69.411.087</t>
   </si>
 </sst>
 </file>
@@ -662,12 +672,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -743,7 +759,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -840,6 +856,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -868,6 +891,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1363,15 +1387,15 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
     </row>
     <row r="8" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1380,29 +1404,29 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="59"/>
+      <c r="B10" s="62"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="J12" s="60" t="s">
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="J12" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="60"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="60"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="63"/>
     </row>
     <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
@@ -1443,7 +1467,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="64" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
@@ -1490,7 +1514,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
+      <c r="A15" s="64"/>
       <c r="B15" t="s">
         <v>84</v>
       </c>
@@ -1565,7 +1589,7 @@
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="64" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
@@ -1612,7 +1636,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
+      <c r="A19" s="64"/>
       <c r="B19" t="s">
         <v>80</v>
       </c>
@@ -1687,7 +1711,7 @@
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="64" t="s">
         <v>81</v>
       </c>
       <c r="B22" t="s">
@@ -1734,7 +1758,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="61"/>
+      <c r="A23" s="64"/>
       <c r="B23" t="s">
         <v>83</v>
       </c>
@@ -1785,10 +1809,10 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="59"/>
+      <c r="B32" s="62"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -1833,6 +1857,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
+  <sheetPr codeName="Tabelle5"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1"/>
@@ -1842,7 +1876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1"/>
@@ -2365,21 +2399,21 @@
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="D40" s="64" t="s">
+      <c r="D40" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64" t="s">
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="K40" s="64"/>
-      <c r="L40" s="64"/>
-      <c r="M40" s="64"/>
-      <c r="N40" s="64"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="67"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
@@ -2420,7 +2454,7 @@
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="65" t="s">
+      <c r="A42" s="68" t="s">
         <v>104</v>
       </c>
       <c r="B42" s="56" t="s">
@@ -2482,7 +2516,7 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="67"/>
+      <c r="A43" s="70"/>
       <c r="B43" s="15" t="s">
         <v>110</v>
       </c>
@@ -2523,7 +2557,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="66"/>
+      <c r="A44" s="69"/>
       <c r="B44" s="16" t="s">
         <v>111</v>
       </c>
@@ -2586,7 +2620,7 @@
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="65" t="s">
+      <c r="A46" s="68" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="19" t="s">
@@ -2640,7 +2674,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="67"/>
+      <c r="A47" s="70"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
@@ -2698,7 +2732,7 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="67"/>
+      <c r="A48" s="70"/>
       <c r="B48" s="15" t="s">
         <v>113</v>
       </c>
@@ -2723,7 +2757,7 @@
       <c r="O48" s="15"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="66"/>
+      <c r="A49" s="69"/>
       <c r="B49" s="22" t="s">
         <v>90</v>
       </c>
@@ -2748,7 +2782,7 @@
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="65" t="s">
+      <c r="A50" s="68" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="19" t="s">
@@ -2802,7 +2836,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="67"/>
+      <c r="A51" s="70"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
@@ -2860,7 +2894,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="67"/>
+      <c r="A52" s="70"/>
       <c r="B52" s="15" t="s">
         <v>113</v>
       </c>
@@ -2885,7 +2919,7 @@
       <c r="O52" s="15"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="69"/>
       <c r="B53" s="22" t="s">
         <v>137</v>
       </c>
@@ -2910,7 +2944,7 @@
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="65" t="s">
+      <c r="A54" s="68" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="19" t="s">
@@ -2964,7 +2998,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="67"/>
+      <c r="A55" s="70"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
@@ -3022,7 +3056,7 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="67"/>
+      <c r="A56" s="70"/>
       <c r="B56" s="15" t="s">
         <v>113</v>
       </c>
@@ -3047,7 +3081,7 @@
       <c r="O56" s="15"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
+      <c r="A57" s="69"/>
       <c r="B57" s="22" t="s">
         <v>138</v>
       </c>
@@ -3072,7 +3106,7 @@
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="65" t="s">
+      <c r="A58" s="68" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="19" t="s">
@@ -3126,7 +3160,7 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="67"/>
+      <c r="A59" s="70"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
@@ -3184,7 +3218,7 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="67"/>
+      <c r="A60" s="70"/>
       <c r="B60" s="15" t="s">
         <v>113</v>
       </c>
@@ -3209,7 +3243,7 @@
       <c r="O60" s="15"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
+      <c r="A61" s="69"/>
       <c r="B61" s="22" t="s">
         <v>139</v>
       </c>
@@ -3234,7 +3268,7 @@
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="65" t="s">
+      <c r="A62" s="68" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -3286,7 +3320,7 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="61"/>
+      <c r="A63" s="64"/>
       <c r="B63" s="34" t="s">
         <v>114</v>
       </c>
@@ -3336,7 +3370,7 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="61"/>
+      <c r="A64" s="64"/>
       <c r="B64" s="15" t="s">
         <v>113</v>
       </c>
@@ -3351,7 +3385,7 @@
       <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
+      <c r="A65" s="69"/>
       <c r="B65" s="47" t="s">
         <v>96</v>
       </c>
@@ -3452,7 +3486,7 @@
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="65" t="s">
+      <c r="A69" s="68" t="s">
         <v>104</v>
       </c>
       <c r="B69" s="20" t="s">
@@ -3506,7 +3540,7 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="67"/>
+      <c r="A70" s="70"/>
       <c r="B70" s="15" t="s">
         <v>110</v>
       </c>
@@ -3545,7 +3579,7 @@
       <c r="O70" s="15"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
+      <c r="A71" s="69"/>
       <c r="B71" s="16" t="s">
         <v>111</v>
       </c>
@@ -3617,7 +3651,7 @@
       <c r="O72" s="15"/>
     </row>
     <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="62" t="s">
+      <c r="A73" s="65" t="s">
         <v>53</v>
       </c>
       <c r="B73" s="4" t="s">
@@ -3665,7 +3699,7 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="62"/>
+      <c r="A74" s="65"/>
       <c r="B74" s="34" t="s">
         <v>114</v>
       </c>
@@ -3711,7 +3745,7 @@
       </c>
     </row>
     <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="62"/>
+      <c r="A75" s="65"/>
       <c r="B75" s="15" t="s">
         <v>113</v>
       </c>
@@ -3725,7 +3759,7 @@
       </c>
     </row>
     <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="63"/>
+      <c r="A76" s="66"/>
       <c r="B76" s="47" t="s">
         <v>96</v>
       </c>
@@ -3821,6 +3855,1973 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73CD4A7B-5043-4ACD-943E-75F29DF344B2}">
+  <dimension ref="A1:U82"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="56.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="39.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="58" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1.4250000000000001E-3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4.1700000000000001E-3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.6857E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>6.8123000000000003E-2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.278499</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.63092800000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="2">
+        <v>8.5990000000000007E-3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3.1836999999999997E-2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.14993899999999999</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.37795099999999998</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.431674</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="C12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="6">
+        <f>Frontend!$H$15*C8</f>
+        <v>14817.435000000001</v>
+      </c>
+      <c r="D13" s="6">
+        <f>Frontend!$H$15*D8</f>
+        <v>43360.493999999999</v>
+      </c>
+      <c r="E13" s="6">
+        <f>Frontend!$H$15*E8</f>
+        <v>175282.45740000001</v>
+      </c>
+      <c r="F13" s="6">
+        <f>Frontend!$H$15*F8</f>
+        <v>708356.57860000001</v>
+      </c>
+      <c r="G13" s="6">
+        <f>Frontend!$H$15*G8</f>
+        <v>2895888.3018</v>
+      </c>
+      <c r="H13" s="6">
+        <f>Frontend!$H$15*H8</f>
+        <v>6560515.5296</v>
+      </c>
+      <c r="I13" s="6">
+        <f>SUM(C13:H13)</f>
+        <v>10398220.796399999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="6">
+        <f>Frontend!$O$15*C9</f>
+        <v>64582.789500000006</v>
+      </c>
+      <c r="D14" s="6">
+        <f>Frontend!$O$15*D9</f>
+        <v>239111.78849999997</v>
+      </c>
+      <c r="E14" s="6">
+        <f>Frontend!$O$15*E9</f>
+        <v>1126116.8595</v>
+      </c>
+      <c r="F14" s="6">
+        <f>Frontend!$O$15*F9</f>
+        <v>2838600.9855</v>
+      </c>
+      <c r="G14" s="6">
+        <f>Frontend!$O$15*G9</f>
+        <v>3242087.577</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="6">
+        <f>SUM(C14:G14)</f>
+        <v>7510500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="8">
+        <f>Frontend!$H$15+I13</f>
+        <v>20796420.796399999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="8">
+        <f>Frontend!$O$15+I14</f>
+        <v>15021000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="58" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" t="s">
+        <v>87</v>
+      </c>
+      <c r="J29" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29" t="s">
+        <v>70</v>
+      </c>
+      <c r="M29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" s="34">
+        <v>45</v>
+      </c>
+      <c r="J30">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I31" s="34">
+        <v>40</v>
+      </c>
+      <c r="J31">
+        <v>0.01</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="34">
+        <v>45</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33">
+        <v>45</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" t="s">
+        <v>49</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34">
+        <v>45</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35">
+        <v>53</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C40" s="15"/>
+      <c r="D40" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="67"/>
+    </row>
+    <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D41" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="20"/>
+      <c r="D42" s="57">
+        <f>SUM(E42:O42)</f>
+        <v>20796420.796399999</v>
+      </c>
+      <c r="E42" s="21">
+        <f t="shared" ref="E42:J42" si="0">C13</f>
+        <v>14817.435000000001</v>
+      </c>
+      <c r="F42" s="21">
+        <f t="shared" si="0"/>
+        <v>43360.493999999999</v>
+      </c>
+      <c r="G42" s="21">
+        <f t="shared" si="0"/>
+        <v>175282.45740000001</v>
+      </c>
+      <c r="H42" s="21">
+        <f t="shared" si="0"/>
+        <v>708356.57860000001</v>
+      </c>
+      <c r="I42" s="21">
+        <f t="shared" si="0"/>
+        <v>2895888.3018</v>
+      </c>
+      <c r="J42" s="21">
+        <f t="shared" si="0"/>
+        <v>6560515.5296</v>
+      </c>
+      <c r="K42" s="21">
+        <f>Frontend!C15</f>
+        <v>3762100</v>
+      </c>
+      <c r="L42" s="21">
+        <f>Frontend!D15</f>
+        <v>3050900</v>
+      </c>
+      <c r="M42" s="21">
+        <f>Frontend!E15</f>
+        <v>2479000</v>
+      </c>
+      <c r="N42" s="21">
+        <f>Frontend!F15</f>
+        <v>1006400</v>
+      </c>
+      <c r="O42" s="21">
+        <f>Frontend!G15</f>
+        <v>99800</v>
+      </c>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="8"/>
+      <c r="S42" s="8"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="70"/>
+      <c r="B43" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15">
+        <v>27</v>
+      </c>
+      <c r="F43" s="15">
+        <v>32</v>
+      </c>
+      <c r="G43" s="15">
+        <v>37</v>
+      </c>
+      <c r="H43" s="15">
+        <v>42</v>
+      </c>
+      <c r="I43" s="15">
+        <v>47</v>
+      </c>
+      <c r="J43" s="15">
+        <v>52</v>
+      </c>
+      <c r="K43" s="15">
+        <v>57</v>
+      </c>
+      <c r="L43" s="15">
+        <v>62</v>
+      </c>
+      <c r="M43" s="15">
+        <v>67</v>
+      </c>
+      <c r="N43" s="15">
+        <v>72</v>
+      </c>
+      <c r="O43" s="16">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" s="69"/>
+      <c r="B44" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15">
+        <f t="shared" ref="E44:O44" si="1">E42/$D$42</f>
+        <v>7.1249928750071259E-4</v>
+      </c>
+      <c r="F44" s="15">
+        <f t="shared" si="1"/>
+        <v>2.0849979150020848E-3</v>
+      </c>
+      <c r="G44" s="15">
+        <f t="shared" si="1"/>
+        <v>8.4284915715084289E-3</v>
+      </c>
+      <c r="H44" s="15">
+        <f t="shared" si="1"/>
+        <v>3.4061465938534062E-2</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="1"/>
+        <v>0.13924936075063926</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="1"/>
+        <v>0.31546368453631546</v>
+      </c>
+      <c r="K44" s="15">
+        <f t="shared" si="1"/>
+        <v>0.18090132128174888</v>
+      </c>
+      <c r="L44" s="15">
+        <f t="shared" si="1"/>
+        <v>0.14670312886379619</v>
+      </c>
+      <c r="M44" s="15">
+        <f t="shared" si="1"/>
+        <v>0.11920320444896612</v>
+      </c>
+      <c r="N44" s="15">
+        <f t="shared" si="1"/>
+        <v>4.8392942701669828E-2</v>
+      </c>
+      <c r="O44" s="15">
+        <f t="shared" si="1"/>
+        <v>4.7989027043190075E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20">
+        <f>IF(E43&gt;$I$32, EXP((LN(1.055)/10)*(E43-$I$32)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="F46" s="20">
+        <f t="shared" ref="F46:O46" si="2">IF(F43&gt;$I$32, EXP((LN(1.055)/10)*(F43-$I$32)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="G46" s="20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H46" s="20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I46" s="20">
+        <f t="shared" si="2"/>
+        <v>1.0107656908500073</v>
+      </c>
+      <c r="J46" s="20">
+        <f t="shared" si="2"/>
+        <v>1.0381897140207395</v>
+      </c>
+      <c r="K46" s="20">
+        <f t="shared" si="2"/>
+        <v>1.0663578038467578</v>
+      </c>
+      <c r="L46" s="20">
+        <f t="shared" si="2"/>
+        <v>1.09529014829188</v>
+      </c>
+      <c r="M46" s="20">
+        <f t="shared" si="2"/>
+        <v>1.1250074830583294</v>
+      </c>
+      <c r="N46" s="20">
+        <f t="shared" si="2"/>
+        <v>1.1555311064479334</v>
+      </c>
+      <c r="O46" s="20">
+        <f t="shared" si="2"/>
+        <v>1.1868828946265373</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="70"/>
+      <c r="B47" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="42">
+        <f>SUM(K47:O47)</f>
+        <v>4.9308310609276644E-2</v>
+      </c>
+      <c r="D47" s="15">
+        <f>SUM(E47:O47)</f>
+        <v>6.2854894074549819E-2</v>
+      </c>
+      <c r="E47" s="24">
+        <f>E44*(E46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="24">
+        <f t="shared" ref="F47:O47" si="3">F44*(F46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="24">
+        <f>G44*(G46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="24">
+        <f t="shared" si="3"/>
+        <v>1.4991155689025278E-3</v>
+      </c>
+      <c r="J47" s="24">
+        <f t="shared" si="3"/>
+        <v>1.2047467896370654E-2</v>
+      </c>
+      <c r="K47" s="24">
+        <f t="shared" si="3"/>
+        <v>1.2004214393233608E-2</v>
+      </c>
+      <c r="L47" s="24">
+        <f t="shared" si="3"/>
+        <v>1.3979362904313918E-2</v>
+      </c>
+      <c r="M47" s="24">
+        <f t="shared" si="3"/>
+        <v>1.4901292560652712E-2</v>
+      </c>
+      <c r="N47" s="24">
+        <f t="shared" si="3"/>
+        <v>7.5266079226621535E-3</v>
+      </c>
+      <c r="O47" s="24">
+        <f t="shared" si="3"/>
+        <v>8.9683282841425394E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" s="70"/>
+      <c r="B48" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" s="42">
+        <f>(C47)/(1+C47)</f>
+        <v>4.6991251389828383E-2</v>
+      </c>
+      <c r="D48" s="17">
+        <f>(D47)/(1+D47)</f>
+        <v>5.9137794279320602E-2</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="69"/>
+      <c r="B49" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="43">
+        <f>0.2069215*C48 * 69411087</f>
+        <v>674918.72002453846</v>
+      </c>
+      <c r="D49" s="22">
+        <f>0.2069215*D48 *69411087</f>
+        <v>849375.21856915392</v>
+      </c>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20">
+        <f>IF(E43&gt;$I$33, EXP((LN(1.032)/10)*(E43-$I$33)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="F50" s="20">
+        <f t="shared" ref="F50:O50" si="4">IF(F43&gt;$I$33, EXP((LN(1.032)/10)*(F43-$I$33)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="G50" s="20">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H50" s="20">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I50" s="20">
+        <f t="shared" si="4"/>
+        <v>1.0063196184673233</v>
+      </c>
+      <c r="J50" s="20">
+        <f t="shared" si="4"/>
+        <v>1.0222939440770498</v>
+      </c>
+      <c r="K50" s="20">
+        <f t="shared" si="4"/>
+        <v>1.0385218462582777</v>
+      </c>
+      <c r="L50" s="20">
+        <f t="shared" si="4"/>
+        <v>1.0550073502875155</v>
+      </c>
+      <c r="M50" s="20">
+        <f t="shared" si="4"/>
+        <v>1.0717545453385426</v>
+      </c>
+      <c r="N50" s="20">
+        <f t="shared" si="4"/>
+        <v>1.088767585496716</v>
+      </c>
+      <c r="O50" s="20">
+        <f t="shared" si="4"/>
+        <v>1.1060506907893759</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="70"/>
+      <c r="B51" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="42">
+        <f>SUM(K51:O51)</f>
+        <v>2.8396426647685286E-2</v>
+      </c>
+      <c r="D51" s="15">
+        <f>SUM(E51:O51)</f>
+        <v>3.6309359220840685E-2</v>
+      </c>
+      <c r="E51" s="15">
+        <f>E44*(E50-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="15">
+        <f t="shared" ref="F51:O51" si="5">F44*(F50-1)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="15">
+        <f t="shared" si="5"/>
+        <v>8.8000283176270673E-4</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="5"/>
+        <v>7.0329297413926854E-3</v>
+      </c>
+      <c r="K51" s="15">
+        <f t="shared" si="5"/>
+        <v>6.9686528863348307E-3</v>
+      </c>
+      <c r="L51" s="15">
+        <f t="shared" si="5"/>
+        <v>8.0697503976853574E-3</v>
+      </c>
+      <c r="M51" s="15">
+        <f t="shared" si="5"/>
+        <v>8.5533717381329078E-3</v>
+      </c>
+      <c r="N51" s="15">
+        <f t="shared" si="5"/>
+        <v>4.2957246787081573E-3</v>
+      </c>
+      <c r="O51" s="15">
+        <f t="shared" si="5"/>
+        <v>5.0892694682403491E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="70"/>
+      <c r="B52" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="42">
+        <f>C51/(1+C51)</f>
+        <v>2.7612335002223338E-2</v>
+      </c>
+      <c r="D52" s="15">
+        <f>D51/(1+D51)</f>
+        <v>3.503718160775874E-2</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="69"/>
+      <c r="B53" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="C53" s="43">
+        <f>0.0115708*C52 * 69411087</f>
+        <v>22176.620586640958</v>
+      </c>
+      <c r="D53" s="22">
+        <f>0.0115708*D52* 69411087</f>
+        <v>28139.825294671246</v>
+      </c>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20">
+        <f>IF(E43&gt;$I$34, EXP((LN(1.062)/10)*(E43-$I$34)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="F54" s="20">
+        <f t="shared" ref="F54:O54" si="6">IF(F43&gt;$I$34, EXP((LN(1.062)/10)*(F43-$I$34)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="G54" s="20">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="H54" s="20">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="20">
+        <f t="shared" si="6"/>
+        <v>1.0121034455497457</v>
+      </c>
+      <c r="J54" s="20">
+        <f t="shared" si="6"/>
+        <v>1.043006852485771</v>
+      </c>
+      <c r="K54" s="20">
+        <f t="shared" si="6"/>
+        <v>1.0748538591738301</v>
+      </c>
+      <c r="L54" s="20">
+        <f t="shared" si="6"/>
+        <v>1.1076732773398887</v>
+      </c>
+      <c r="M54" s="20">
+        <f t="shared" si="6"/>
+        <v>1.1414947984426076</v>
+      </c>
+      <c r="N54" s="20">
+        <f t="shared" si="6"/>
+        <v>1.1763490205349618</v>
+      </c>
+      <c r="O54" s="20">
+        <f t="shared" si="6"/>
+        <v>1.2122674759460494</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="70"/>
+      <c r="B55" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="42">
+        <f>SUM(K55:O55)</f>
+        <v>5.5756501106184665E-2</v>
+      </c>
+      <c r="D55" s="15">
+        <f>SUM(E55:O55)</f>
+        <v>7.1008998307338034E-2</v>
+      </c>
+      <c r="E55" s="15">
+        <f>E44*(E54-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="15">
+        <f t="shared" ref="F55:O55" si="7">F44*(F54-1)</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="15">
+        <f t="shared" si="7"/>
+        <v>1.6853970556822639E-3</v>
+      </c>
+      <c r="J55" s="15">
+        <f t="shared" si="7"/>
+        <v>1.3567100145471106E-2</v>
+      </c>
+      <c r="K55" s="15">
+        <f t="shared" si="7"/>
+        <v>1.3541162027583832E-2</v>
+      </c>
+      <c r="L55" s="15">
+        <f t="shared" si="7"/>
+        <v>1.5796006680780964E-2</v>
+      </c>
+      <c r="M55" s="15">
+        <f t="shared" si="7"/>
+        <v>1.6866633387219405E-2</v>
+      </c>
+      <c r="N55" s="15">
+        <f t="shared" si="7"/>
+        <v>8.5340480462440024E-3</v>
+      </c>
+      <c r="O55" s="15">
+        <f t="shared" si="7"/>
+        <v>1.0186509643564665E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="70"/>
+      <c r="B56" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" s="42">
+        <f>C55/(1+C55)</f>
+        <v>5.2811894644044302E-2</v>
+      </c>
+      <c r="D56" s="15">
+        <f>D55/(1+D55)</f>
+        <v>6.6301028674421281E-2</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="69"/>
+      <c r="B57" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" s="43">
+        <f>0.0059261*C56 * 69411087</f>
+        <v>21723.488560717764</v>
+      </c>
+      <c r="D57" s="22">
+        <f>0.0059261*D56 * 69411087</f>
+        <v>27272.06906096173</v>
+      </c>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20">
+        <f>IF(E43&gt;$I$35, EXP((LN(1.08)/10)*(E43-$I$35)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="F58" s="20">
+        <f t="shared" ref="F58:O58" si="8">IF(F43&gt;$I$35, EXP((LN(1.08)/10)*(F43-$I$35)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="G58" s="20">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H58" s="20">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="I58" s="20">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J58" s="20">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K58" s="20">
+        <f t="shared" si="8"/>
+        <v>1.0312631565524872</v>
+      </c>
+      <c r="L58" s="20">
+        <f t="shared" si="8"/>
+        <v>1.0717201098736591</v>
+      </c>
+      <c r="M58" s="20">
+        <f t="shared" si="8"/>
+        <v>1.1137642090766864</v>
+      </c>
+      <c r="N58" s="20">
+        <f t="shared" si="8"/>
+        <v>1.157457718663552</v>
+      </c>
+      <c r="O58" s="20">
+        <f t="shared" si="8"/>
+        <v>1.2028653458028213</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="70"/>
+      <c r="B59" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C59" s="15">
+        <f>SUM(K59:O59)</f>
+        <v>3.8331542536053996E-2</v>
+      </c>
+      <c r="D59" s="42">
+        <f>SUM(E59:O59)</f>
+        <v>3.8331542536053996E-2</v>
+      </c>
+      <c r="E59" s="15">
+        <f>E44*(E58-1)</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="15">
+        <f t="shared" ref="F59:O59" si="9">F44*(F58-1)</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="15">
+        <f t="shared" si="9"/>
+        <v>5.6555463277831062E-3</v>
+      </c>
+      <c r="L59" s="15">
+        <f t="shared" si="9"/>
+        <v>1.0521564520921027E-2</v>
+      </c>
+      <c r="M59" s="15">
+        <f t="shared" si="9"/>
+        <v>1.3561058273543175E-2</v>
+      </c>
+      <c r="N59" s="15">
+        <f t="shared" si="9"/>
+        <v>7.6198423572209177E-3</v>
+      </c>
+      <c r="O59" s="15">
+        <f t="shared" si="9"/>
+        <v>9.7353105658576995E-4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="70"/>
+      <c r="B60" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="15">
+        <f>C59/(1+C59)</f>
+        <v>3.69164770266266E-2</v>
+      </c>
+      <c r="D60" s="42">
+        <f>D59/(1+D59)</f>
+        <v>3.69164770266266E-2</v>
+      </c>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="69"/>
+      <c r="B61" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="22">
+        <f>0.00127695*C60 * 69411087</f>
+        <v>3272.0730232088936</v>
+      </c>
+      <c r="D61" s="43">
+        <f>0.00127695*D60 * 69411087</f>
+        <v>3272.0730232088936</v>
+      </c>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E62" s="21">
+        <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="21">
+        <f t="shared" ref="F62:O62" si="10">IF(F43&gt;$I$30,((78.927 - 3.1162 * F43 + 0.0342 * F43^2)/100),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="21">
+        <f t="shared" si="10"/>
+        <v>8.0134000000000191E-2</v>
+      </c>
+      <c r="J62" s="21">
+        <f t="shared" si="10"/>
+        <v>9.3613999999999892E-2</v>
+      </c>
+      <c r="K62" s="21">
+        <f t="shared" si="10"/>
+        <v>0.1241940000000001</v>
+      </c>
+      <c r="L62" s="21">
+        <f t="shared" si="10"/>
+        <v>0.17187400000000011</v>
+      </c>
+      <c r="M62" s="21">
+        <f t="shared" si="10"/>
+        <v>0.23665399999999978</v>
+      </c>
+      <c r="N62" s="21">
+        <f t="shared" si="10"/>
+        <v>0.31853400000000021</v>
+      </c>
+      <c r="O62" s="21">
+        <f t="shared" si="10"/>
+        <v>0.41751400000000016</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="64"/>
+      <c r="B63" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E63">
+        <f>$E$44*E62</f>
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ref="F63:O63" si="11">$E$44*F62</f>
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="11"/>
+        <v>5.7095417904582238E-5</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="11"/>
+        <v>6.6699908300091627E-5</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="11"/>
+        <v>8.8488136511863564E-5</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="11"/>
+        <v>1.2246010253989754E-4</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="11"/>
+        <v>1.6861580638419349E-4</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="11"/>
+        <v>2.2695524804475212E-4</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="11"/>
+        <v>2.9747842752157261E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="64"/>
+      <c r="B64" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C64">
+        <f>SUM(K63:O63)</f>
+        <v>9.0399772100227928E-4</v>
+      </c>
+      <c r="D64">
+        <f>SUM(E63:O63)</f>
+        <v>1.0277930472069531E-3</v>
+      </c>
+      <c r="E64" s="23"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="69"/>
+      <c r="B65" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="36">
+        <f>C64*$J$30*69411087</f>
+        <v>690.22210906320026</v>
+      </c>
+      <c r="D65" s="36">
+        <f>D64*$J$30*69411087</f>
+        <v>784.74255879444627</v>
+      </c>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="60"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="60"/>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+    </row>
+    <row r="68" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="60"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="O68" s="15"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C69" s="20"/>
+      <c r="D69" s="37">
+        <f>SUM(E69:N69)</f>
+        <v>15021000</v>
+      </c>
+      <c r="E69" s="33">
+        <f>C14</f>
+        <v>64582.789500000006</v>
+      </c>
+      <c r="F69" s="33">
+        <f>D14</f>
+        <v>239111.78849999997</v>
+      </c>
+      <c r="G69" s="33">
+        <f>E14</f>
+        <v>1126116.8595</v>
+      </c>
+      <c r="H69" s="33">
+        <f>F14</f>
+        <v>2838600.9855</v>
+      </c>
+      <c r="I69" s="33">
+        <f>G14</f>
+        <v>3242087.577</v>
+      </c>
+      <c r="J69" s="33">
+        <f>Frontend!J15</f>
+        <v>3383500</v>
+      </c>
+      <c r="K69" s="33">
+        <f>Frontend!K15</f>
+        <v>2682400</v>
+      </c>
+      <c r="L69" s="33">
+        <f>Frontend!L15</f>
+        <v>1283500</v>
+      </c>
+      <c r="M69" s="33">
+        <f>Frontend!M15</f>
+        <v>156200</v>
+      </c>
+      <c r="N69" s="33">
+        <f>Frontend!N15</f>
+        <v>4900</v>
+      </c>
+      <c r="O69" s="15"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="70"/>
+      <c r="B70" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15">
+        <v>27</v>
+      </c>
+      <c r="F70" s="15">
+        <v>32</v>
+      </c>
+      <c r="G70" s="15">
+        <v>37</v>
+      </c>
+      <c r="H70" s="15">
+        <v>42</v>
+      </c>
+      <c r="I70" s="15">
+        <v>47</v>
+      </c>
+      <c r="J70" s="15">
+        <v>52</v>
+      </c>
+      <c r="K70" s="15">
+        <v>57</v>
+      </c>
+      <c r="L70" s="15">
+        <v>62</v>
+      </c>
+      <c r="M70" s="15">
+        <v>67</v>
+      </c>
+      <c r="N70" s="16">
+        <v>72</v>
+      </c>
+      <c r="O70" s="15"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="69"/>
+      <c r="B71" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="18"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="32">
+        <f>E69/$D$69</f>
+        <v>4.2995000000000004E-3</v>
+      </c>
+      <c r="F71" s="32">
+        <f t="shared" ref="F71:N71" si="12">F69/$D$69</f>
+        <v>1.5918499999999999E-2</v>
+      </c>
+      <c r="G71" s="32">
+        <f t="shared" si="12"/>
+        <v>7.4969499999999994E-2</v>
+      </c>
+      <c r="H71" s="32">
+        <f t="shared" si="12"/>
+        <v>0.18897549999999999</v>
+      </c>
+      <c r="I71" s="32">
+        <f t="shared" si="12"/>
+        <v>0.215837</v>
+      </c>
+      <c r="J71" s="32">
+        <f t="shared" si="12"/>
+        <v>0.2252513148259104</v>
+      </c>
+      <c r="K71" s="32">
+        <f t="shared" si="12"/>
+        <v>0.17857665934358566</v>
+      </c>
+      <c r="L71" s="32">
+        <f t="shared" si="12"/>
+        <v>8.5447040809533317E-2</v>
+      </c>
+      <c r="M71" s="32">
+        <f t="shared" si="12"/>
+        <v>1.0398775048265762E-2</v>
+      </c>
+      <c r="N71" s="32">
+        <f t="shared" si="12"/>
+        <v>3.2620997270487985E-4</v>
+      </c>
+      <c r="O71" s="15"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" s="40"/>
+      <c r="C72" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="41"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="41"/>
+      <c r="J72" s="41"/>
+      <c r="K72" s="41"/>
+      <c r="L72" s="41"/>
+      <c r="M72" s="41"/>
+      <c r="N72" s="41"/>
+      <c r="O72" s="15"/>
+    </row>
+    <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E73" s="34">
+        <f>IF(E70&gt;$I$31,((19.4312 - 0.9336 *  E70 + 0.0126 *  E70^2)/100),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="34">
+        <f t="shared" ref="F73:N73" si="13">IF(F70&gt;$I$31,((19.4312 - 0.9336 *  F70 + 0.0126 *  F70^2)/100),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="34">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="34">
+        <f t="shared" si="13"/>
+        <v>2.4464000000000041E-2</v>
+      </c>
+      <c r="I73" s="34">
+        <f t="shared" si="13"/>
+        <v>3.3854000000000044E-2</v>
+      </c>
+      <c r="J73" s="34">
+        <f t="shared" si="13"/>
+        <v>4.9544000000000032E-2</v>
+      </c>
+      <c r="K73" s="34">
+        <f t="shared" si="13"/>
+        <v>7.1534000000000125E-2</v>
+      </c>
+      <c r="L73" s="34">
+        <f t="shared" si="13"/>
+        <v>9.9824000000000052E-2</v>
+      </c>
+      <c r="M73" s="34">
+        <f t="shared" si="13"/>
+        <v>0.13441399999999995</v>
+      </c>
+      <c r="N73" s="34">
+        <f t="shared" si="13"/>
+        <v>0.17530400000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="65"/>
+      <c r="B74" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="34">
+        <f>E73*E71</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="34">
+        <f t="shared" ref="F74:N74" si="14">F73*F71</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="34">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="34">
+        <f t="shared" si="14"/>
+        <v>4.6230966320000072E-3</v>
+      </c>
+      <c r="I74" s="34">
+        <f t="shared" si="14"/>
+        <v>7.3069457980000094E-3</v>
+      </c>
+      <c r="J74" s="34">
+        <f t="shared" si="14"/>
+        <v>1.1159851141734912E-2</v>
+      </c>
+      <c r="K74" s="34">
+        <f t="shared" si="14"/>
+        <v>1.2774302749484078E-2</v>
+      </c>
+      <c r="L74" s="34">
+        <f t="shared" si="14"/>
+        <v>8.5296654017708584E-3</v>
+      </c>
+      <c r="M74" s="34">
+        <f t="shared" si="14"/>
+        <v>1.3977409493375935E-3</v>
+      </c>
+      <c r="N74" s="34">
+        <f t="shared" si="14"/>
+        <v>5.718591305505626E-5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="65"/>
+      <c r="B75" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="34">
+        <f>SUM(J74:N74)</f>
+        <v>3.3918746155382498E-2</v>
+      </c>
+      <c r="D75" s="34">
+        <f>SUM(E74:N74)</f>
+        <v>4.5848788585382522E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="66"/>
+      <c r="B76" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="36">
+        <f>C75*J31*69411087</f>
+        <v>23543.370403221699</v>
+      </c>
+      <c r="D76" s="36">
+        <f>D75*J31*69411087</f>
+        <v>31824.142533445931</v>
+      </c>
+      <c r="E76" s="35"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35"/>
+      <c r="I76" s="35"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="35"/>
+      <c r="L76" s="35"/>
+      <c r="M76" s="35"/>
+      <c r="N76" s="35"/>
+      <c r="O76" s="24"/>
+    </row>
+    <row r="79" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>102</v>
+      </c>
+      <c r="D80" t="s">
+        <v>103</v>
+      </c>
+      <c r="E80" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B81" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C81" s="48">
+        <f>C61+C65+C76</f>
+        <v>27505.665535493794</v>
+      </c>
+      <c r="D81" s="48">
+        <f>D49+D53+D57+D65+D76</f>
+        <v>937395.99801702728</v>
+      </c>
+      <c r="E81" s="45">
+        <f>D81-C81</f>
+        <v>909890.33248153352</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B82" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C82" s="49">
+        <f>C81*70000</f>
+        <v>1925396587.4845655</v>
+      </c>
+      <c r="D82" s="49">
+        <f>D81*70000</f>
+        <v>65617719861.19191</v>
+      </c>
+      <c r="E82" s="46">
+        <f>D82-C82</f>
+        <v>63692323273.707344</v>
+      </c>
+      <c r="F82" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="J40:N40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3900,7 +5901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8C717-7812-4473-9D8B-3495A5B0BB7F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3910,7 +5911,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3933,7 +5934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3BA502-77FB-4AA9-A654-F467290EB112}">
   <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G13"/>
@@ -4122,7 +6123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601D2B11-F41E-4CFB-A90C-BC8CA1A15B8D}">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1"/>
@@ -4132,7 +6133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B738CEAF-BA8D-46A4-B41F-A105DC1BD636}">
   <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1"/>
@@ -4140,14 +6141,4 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
-  <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <workbookPr codeName="DieseArbeitsmappe"/>
+  <workbookPr dateCompatibility="0" codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC11835-95AE-4FCD-86BD-294E2959B9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63AA3E00-C5FC-4679-9AD1-7FA2B893E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="158">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="299" uniqueCount="158">
   <si>
     <t>L_den</t>
   </si>
@@ -613,7 +616,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.000000"/>
@@ -785,15 +788,15 @@
   </fills>
   <borders count="14">
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="thick">
         <color theme="4"/>
@@ -801,8 +804,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="thick">
         <color theme="4" tint="0.499984740745262"/>
@@ -810,8 +813,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.39997558519241921"/>
@@ -819,8 +822,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -828,8 +831,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -837,8 +840,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -848,19 +851,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </start>
+      <end/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </start>
+      <end/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -868,10 +871,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </start>
+      <end/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -879,10 +882,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
+      </start>
+      <end/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -892,10 +895,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
+      <start style="thick">
         <color rgb="FFFF0000"/>
-      </left>
-      <right/>
+      </start>
+      <end/>
       <top style="thick">
         <color rgb="FFFF0000"/>
       </top>
@@ -905,8 +908,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top style="thick">
         <color rgb="FFFF0000"/>
       </top>
@@ -916,10 +919,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
+      <start/>
+      <end style="thick">
         <color rgb="FFFF0000"/>
-      </right>
+      </end>
       <top style="thick">
         <color rgb="FFFF0000"/>
       </top>
@@ -1125,6 +1128,27 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1168,27 +1192,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1212,7 +1215,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1240,7 +1243,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1284,7 +1287,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1305,7 +1308,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1333,7 +1336,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1377,7 +1380,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1398,7 +1401,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1517,25 +1520,25 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:lumMod val="110%"/>
+                <a:satMod val="105%"/>
+                <a:tint val="67%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:lumMod val="105%"/>
+                <a:satMod val="103%"/>
+                <a:tint val="73%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:lumMod val="105%"/>
+                <a:satMod val="109%"/>
+                <a:tint val="81%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1543,25 +1546,25 @@
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:satMod val="103%"/>
+                <a:lumMod val="102%"/>
+                <a:tint val="94%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:satMod val="110%"/>
+                <a:lumMod val="100%"/>
+                <a:shade val="100%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:lumMod val="99%"/>
+                <a:satMod val="120%"/>
+                <a:shade val="78%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1574,21 +1577,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1602,7 +1605,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="63%"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -1614,32 +1617,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
+            <a:tint val="95%"/>
+            <a:satMod val="170%"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="93%"/>
+                <a:satMod val="150%"/>
+                <a:shade val="98%"/>
+                <a:lumMod val="102%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="98%"/>
+                <a:satMod val="130%"/>
+                <a:shade val="90%"/>
+                <a:lumMod val="103%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="63%"/>
+                <a:satMod val="120%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1659,7 +1662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11457340-40AB-4C39-9488-F3F169CC7A0E}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11457340-40AB-4C39-9488-F3F169CC7A0E}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1668,7 +1671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1678,7 +1681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1688,7 +1691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1711,7 +1714,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
   <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1739,15 +1742,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1756,10 +1759,10 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="121" t="s">
+      <c r="A10" s="134" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="121"/>
+      <c r="B10" s="134"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1769,22 +1772,22 @@
       <c r="B12" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="123" t="s">
+      <c r="D12" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="123"/>
-      <c r="K12" s="119" t="s">
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="K12" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="L12" s="119"/>
-      <c r="M12" s="119"/>
-      <c r="N12" s="119"/>
-      <c r="O12" s="119"/>
-      <c r="P12" s="119"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="132"/>
+      <c r="N12" s="132"/>
+      <c r="O12" s="132"/>
+      <c r="P12" s="132"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="110"/>
@@ -1827,7 +1830,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="122" t="s">
+      <c r="A14" s="135" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="110" t="s">
@@ -1874,47 +1877,47 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="122"/>
-      <c r="B15" s="134" t="s">
+      <c r="A15" s="135"/>
+      <c r="B15" s="119" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="15"/>
-      <c r="D15" s="135">
+      <c r="D15" s="120">
         <v>3762100</v>
       </c>
-      <c r="E15" s="135">
+      <c r="E15" s="120">
         <v>3050900</v>
       </c>
-      <c r="F15" s="135">
+      <c r="F15" s="120">
         <v>2479000</v>
       </c>
-      <c r="G15" s="135">
+      <c r="G15" s="120">
         <v>1006400</v>
       </c>
-      <c r="H15" s="135">
+      <c r="H15" s="120">
         <v>99800</v>
       </c>
-      <c r="I15" s="135">
+      <c r="I15" s="120">
         <f t="shared" ref="I15:I23" si="0">SUM(D15:H15)</f>
         <v>10398200</v>
       </c>
-      <c r="J15" s="136"/>
-      <c r="K15" s="137">
+      <c r="J15" s="121"/>
+      <c r="K15" s="122">
         <v>3383500</v>
       </c>
-      <c r="L15" s="137">
+      <c r="L15" s="122">
         <v>2682400</v>
       </c>
-      <c r="M15" s="137">
+      <c r="M15" s="122">
         <v>1283500</v>
       </c>
-      <c r="N15" s="137">
+      <c r="N15" s="122">
         <v>156200</v>
       </c>
-      <c r="O15" s="137">
+      <c r="O15" s="122">
         <v>4900</v>
       </c>
-      <c r="P15" s="137">
+      <c r="P15" s="122">
         <f t="shared" ref="P15:P23" si="1">SUM(K15:O15)</f>
         <v>7510500</v>
       </c>
@@ -1954,7 +1957,7 @@
       <c r="P17" s="109"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="122" t="s">
+      <c r="A18" s="135" t="s">
         <v>78</v>
       </c>
       <c r="B18" s="110" t="s">
@@ -2001,7 +2004,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="122"/>
+      <c r="A19" s="135"/>
       <c r="B19" s="110" t="s">
         <v>80</v>
       </c>
@@ -2065,7 +2068,7 @@
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="110"/>
       <c r="B21" s="110"/>
-      <c r="D21" s="138"/>
+      <c r="D21" s="123"/>
       <c r="E21" s="106"/>
       <c r="F21" s="106"/>
       <c r="G21" s="106"/>
@@ -2080,7 +2083,7 @@
       <c r="P21" s="109"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="122" t="s">
+      <c r="A22" s="135" t="s">
         <v>81</v>
       </c>
       <c r="B22" s="110" t="s">
@@ -2127,7 +2130,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="122"/>
+      <c r="A23" s="135"/>
       <c r="B23" s="110" t="s">
         <v>83</v>
       </c>
@@ -2178,10 +2181,10 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="121" t="s">
+      <c r="A32" s="134" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="121"/>
+      <c r="B32" s="134"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -2235,11 +2238,11 @@
       <c r="B39" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="139">
+      <c r="C39" s="124">
         <f>'Agglomeration road'!C79</f>
         <v>27420.859000423719</v>
       </c>
-      <c r="D39" s="141">
+      <c r="D39" s="126">
         <f>'Agglomeration road'!D79</f>
         <v>308626.30242553435</v>
       </c>
@@ -2248,11 +2251,11 @@
       <c r="B40" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="140">
+      <c r="C40" s="125">
         <f>'Agglomeration road'!C80</f>
         <v>1919460130.0296605</v>
       </c>
-      <c r="D40" s="142">
+      <c r="D40" s="127">
         <f>'Agglomeration road'!D80</f>
         <v>21603841169.787403</v>
       </c>
@@ -2274,7 +2277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCA578C-B553-47BE-9A2E-931A94425EB8}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCA578C-B553-47BE-9A2E-931A94425EB8}">
   <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2302,15 +2305,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -2319,10 +2322,10 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="121" t="s">
+      <c r="A10" s="134" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="121"/>
+      <c r="B10" s="134"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -2332,22 +2335,22 @@
       <c r="B12" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="123" t="s">
+      <c r="D12" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="123"/>
-      <c r="K12" s="119" t="s">
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="K12" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="L12" s="119"/>
-      <c r="M12" s="119"/>
-      <c r="N12" s="119"/>
-      <c r="O12" s="119"/>
-      <c r="P12" s="119"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="132"/>
+      <c r="N12" s="132"/>
+      <c r="O12" s="132"/>
+      <c r="P12" s="132"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="110"/>
@@ -2390,7 +2393,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="122" t="s">
+      <c r="A14" s="135" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="110" t="s">
@@ -2437,7 +2440,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="122"/>
+      <c r="A15" s="135"/>
       <c r="B15" s="111" t="s">
         <v>84</v>
       </c>
@@ -2517,7 +2520,7 @@
       <c r="P17" s="109"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="122" t="s">
+      <c r="A18" s="135" t="s">
         <v>78</v>
       </c>
       <c r="B18" s="110" t="s">
@@ -2564,7 +2567,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="122"/>
+      <c r="A19" s="135"/>
       <c r="B19" s="110" t="s">
         <v>80</v>
       </c>
@@ -2628,7 +2631,7 @@
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="110"/>
       <c r="B21" s="110"/>
-      <c r="D21" s="138"/>
+      <c r="D21" s="123"/>
       <c r="E21" s="106"/>
       <c r="F21" s="106"/>
       <c r="G21" s="106"/>
@@ -2643,7 +2646,7 @@
       <c r="P21" s="109"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="122" t="s">
+      <c r="A22" s="135" t="s">
         <v>81</v>
       </c>
       <c r="B22" s="110" t="s">
@@ -2690,7 +2693,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="122"/>
+      <c r="A23" s="135"/>
       <c r="B23" s="110" t="s">
         <v>83</v>
       </c>
@@ -2741,10 +2744,10 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="121" t="s">
+      <c r="A32" s="134" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="121"/>
+      <c r="B32" s="134"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -2798,10 +2801,10 @@
       <c r="B39" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="143" t="s">
+      <c r="C39" s="128" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="144" t="s">
+      <c r="D39" s="129" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2809,23 +2812,23 @@
       <c r="B40" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="145" t="s">
+      <c r="C40" s="130" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="146" t="s">
+      <c r="D40" s="131" t="s">
         <v>156</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:A19"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D12:I12"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2833,7 +2836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3345,21 +3348,21 @@
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="E40" s="124" t="s">
+      <c r="E40" s="137" t="s">
         <v>91</v>
       </c>
-      <c r="F40" s="124"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="124"/>
-      <c r="J40" s="124"/>
-      <c r="K40" s="125" t="s">
+      <c r="F40" s="137"/>
+      <c r="G40" s="137"/>
+      <c r="H40" s="137"/>
+      <c r="I40" s="137"/>
+      <c r="J40" s="137"/>
+      <c r="K40" s="138" t="s">
         <v>90</v>
       </c>
-      <c r="L40" s="126"/>
-      <c r="M40" s="126"/>
-      <c r="N40" s="126"/>
-      <c r="O40" s="126"/>
+      <c r="L40" s="139"/>
+      <c r="M40" s="139"/>
+      <c r="N40" s="139"/>
+      <c r="O40" s="139"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
@@ -3400,7 +3403,7 @@
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="131" t="s">
+      <c r="A42" s="144" t="s">
         <v>101</v>
       </c>
       <c r="B42" s="43" t="s">
@@ -3462,7 +3465,7 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="132"/>
+      <c r="A43" s="145"/>
       <c r="B43" s="15" t="s">
         <v>107</v>
       </c>
@@ -3503,7 +3506,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="133"/>
+      <c r="A44" s="146"/>
       <c r="B44" s="19" t="s">
         <v>108</v>
       </c>
@@ -3577,7 +3580,7 @@
       <c r="O45" s="57"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="131" t="s">
+      <c r="A46" s="144" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="17" t="s">
@@ -3631,7 +3634,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="132"/>
+      <c r="A47" s="145"/>
       <c r="B47" s="15" t="s">
         <v>88</v>
       </c>
@@ -3689,7 +3692,7 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="132"/>
+      <c r="A48" s="145"/>
       <c r="B48" s="15" t="s">
         <v>110</v>
       </c>
@@ -3714,7 +3717,7 @@
       <c r="O48" s="54"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="133"/>
+      <c r="A49" s="146"/>
       <c r="B49" s="42" t="s">
         <v>145</v>
       </c>
@@ -3739,7 +3742,7 @@
       <c r="O49" s="61"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="131" t="s">
+      <c r="A50" s="144" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="17" t="s">
@@ -3793,7 +3796,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="132"/>
+      <c r="A51" s="145"/>
       <c r="B51" s="15" t="s">
         <v>88</v>
       </c>
@@ -3851,7 +3854,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="132"/>
+      <c r="A52" s="145"/>
       <c r="B52" s="15" t="s">
         <v>110</v>
       </c>
@@ -3876,7 +3879,7 @@
       <c r="O52" s="54"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="133"/>
+      <c r="A53" s="146"/>
       <c r="B53" s="42" t="s">
         <v>132</v>
       </c>
@@ -3901,7 +3904,7 @@
       <c r="O53" s="61"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="131" t="s">
+      <c r="A54" s="144" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="17" t="s">
@@ -3955,7 +3958,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="132"/>
+      <c r="A55" s="145"/>
       <c r="B55" s="15" t="s">
         <v>88</v>
       </c>
@@ -4013,7 +4016,7 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="132"/>
+      <c r="A56" s="145"/>
       <c r="B56" s="15" t="s">
         <v>110</v>
       </c>
@@ -4038,7 +4041,7 @@
       <c r="O56" s="54"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="133"/>
+      <c r="A57" s="146"/>
       <c r="B57" s="42" t="s">
         <v>133</v>
       </c>
@@ -4063,7 +4066,7 @@
       <c r="O57" s="61"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="131" t="s">
+      <c r="A58" s="144" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="17" t="s">
@@ -4117,7 +4120,7 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="132"/>
+      <c r="A59" s="145"/>
       <c r="B59" s="15" t="s">
         <v>88</v>
       </c>
@@ -4175,7 +4178,7 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="132"/>
+      <c r="A60" s="145"/>
       <c r="B60" s="15" t="s">
         <v>110</v>
       </c>
@@ -4200,7 +4203,7 @@
       <c r="O60" s="54"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="133"/>
+      <c r="A61" s="146"/>
       <c r="B61" s="42" t="s">
         <v>134</v>
       </c>
@@ -4225,7 +4228,7 @@
       <c r="O61" s="61"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="129" t="s">
+      <c r="A62" s="142" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="27" t="s">
@@ -4279,7 +4282,7 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="130"/>
+      <c r="A63" s="143"/>
       <c r="B63" s="27" t="s">
         <v>146</v>
       </c>
@@ -4337,7 +4340,7 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="128"/>
+      <c r="A64" s="141"/>
       <c r="B64" s="44" t="s">
         <v>147</v>
       </c>
@@ -4383,20 +4386,20 @@
       <c r="B66" s="23"/>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
-      <c r="E66" s="124" t="s">
+      <c r="E66" s="137" t="s">
         <v>92</v>
       </c>
-      <c r="F66" s="124"/>
-      <c r="G66" s="124"/>
-      <c r="H66" s="124"/>
-      <c r="I66" s="124"/>
-      <c r="J66" s="125" t="s">
+      <c r="F66" s="137"/>
+      <c r="G66" s="137"/>
+      <c r="H66" s="137"/>
+      <c r="I66" s="137"/>
+      <c r="J66" s="138" t="s">
         <v>93</v>
       </c>
-      <c r="K66" s="126"/>
-      <c r="L66" s="126"/>
-      <c r="M66" s="126"/>
-      <c r="N66" s="126"/>
+      <c r="K66" s="139"/>
+      <c r="L66" s="139"/>
+      <c r="M66" s="139"/>
+      <c r="N66" s="139"/>
       <c r="O66" s="24"/>
     </row>
     <row r="67" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -4439,7 +4442,7 @@
       <c r="O67" s="15"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="131" t="s">
+      <c r="A68" s="144" t="s">
         <v>101</v>
       </c>
       <c r="B68" s="18" t="s">
@@ -4493,7 +4496,7 @@
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="132"/>
+      <c r="A69" s="145"/>
       <c r="B69" s="15" t="s">
         <v>107</v>
       </c>
@@ -4532,7 +4535,7 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="133"/>
+      <c r="A70" s="146"/>
       <c r="B70" s="19" t="s">
         <v>108</v>
       </c>
@@ -4604,7 +4607,7 @@
       <c r="O71" s="15"/>
     </row>
     <row r="72" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="127" t="s">
+      <c r="A72" s="140" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="27" t="s">
@@ -4654,7 +4657,7 @@
       </c>
     </row>
     <row r="73" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="127"/>
+      <c r="A73" s="140"/>
       <c r="B73" s="27" t="s">
         <v>146</v>
       </c>
@@ -4708,7 +4711,7 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="128"/>
+      <c r="A74" s="141"/>
       <c r="B74" s="44" t="s">
         <v>148</v>
       </c>
@@ -4858,7 +4861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4938,7 +4941,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8C717-7812-4473-9D8B-3495A5B0BB7F}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8C717-7812-4473-9D8B-3495A5B0BB7F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -4948,7 +4951,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3BA502-77FB-4AA9-A654-F467290EB112}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3BA502-77FB-4AA9-A654-F467290EB112}">
   <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5137,7 +5140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601D2B11-F41E-4CFB-A90C-BC8CA1A15B8D}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601D2B11-F41E-4CFB-A90C-BC8CA1A15B8D}">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5147,7 +5150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
   <sheetPr codeName="Tabelle5"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
